--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.80914493823274</v>
+        <v>5.656486052462821</v>
       </c>
       <c r="D2" t="n">
-        <v>34.48473142956657</v>
+        <v>5.603768857304568</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F2" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.47740578945384</v>
+        <v>2.51507844078625</v>
       </c>
       <c r="D3" t="n">
-        <v>15.0481173898371</v>
+        <v>2.445319075848528</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F3" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.63963973351921</v>
+        <v>2.703941456696872</v>
       </c>
       <c r="D4" t="n">
-        <v>17.42836742631166</v>
+        <v>2.832109706775645</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F4" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.69028152957147</v>
+        <v>5.799670748555364</v>
       </c>
       <c r="D5" t="n">
-        <v>34.86359885006867</v>
+        <v>5.665334813136159</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F5" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.79782951535865</v>
+        <v>4.842147296245781</v>
       </c>
       <c r="D6" t="n">
-        <v>29.00537401112163</v>
+        <v>4.713373276807265</v>
       </c>
       <c r="E6" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F6" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.09354816701725</v>
+        <v>3.590201577140303</v>
       </c>
       <c r="D7" t="n">
-        <v>22.09644970623127</v>
+        <v>3.590673077262581</v>
       </c>
       <c r="E7" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F7" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.84805080895702</v>
+        <v>5.012808256455516</v>
       </c>
       <c r="D8" t="n">
-        <v>31.03917780120726</v>
+        <v>5.04386639269618</v>
       </c>
       <c r="E8" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F8" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.65159689679469</v>
+        <v>5.793384495729136</v>
       </c>
       <c r="D9" t="n">
-        <v>35.4101834440495</v>
+        <v>5.754154809658044</v>
       </c>
       <c r="E9" t="n">
-        <v>7.8663471879511</v>
+        <v>1.278281418042054</v>
       </c>
       <c r="F9" t="n">
-        <v>7.632241157839847</v>
+        <v>1.240239188148975</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
